--- a/data/education/working/fod_earn_edu_att.xlsx
+++ b/data/education/working/fod_earn_edu_att.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,992 +468,960 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Field of Degree</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Total Population </t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Bachelor's Degree Only</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Advanced Degree</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Population 25 to 64 with a Bachelor's degree or higher with earnings1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>74150</v>
+      </c>
+      <c r="C2" t="n">
+        <v>165.7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>66410</v>
+      </c>
+      <c r="E2" t="n">
+        <v>202.2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>86120</v>
+      </c>
+      <c r="G2" t="n">
+        <v>246.7</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Estimate </t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOE </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Estimate </t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOE </t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Estimate </t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOE </t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science and Engineering Degrees </t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Population 25 to 64 with a Bachelor's degree or higher with earnings1</t>
+          <t xml:space="preserve">Computer Science </t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74150</v>
+        <v>108500</v>
       </c>
       <c r="C4" t="n">
-        <v>165.7</v>
+        <v>1597</v>
       </c>
       <c r="D4" t="n">
-        <v>66410</v>
+        <v>101600</v>
       </c>
       <c r="E4" t="n">
-        <v>202.2</v>
+        <v>867.3</v>
       </c>
       <c r="F4" t="n">
-        <v>86120</v>
+        <v>128800</v>
       </c>
       <c r="G4" t="n">
-        <v>246.7</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Science and Engineering Degrees </t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t xml:space="preserve">Engineering </t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>100600</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1031</v>
+      </c>
+      <c r="D5" t="n">
+        <v>90490</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2213</v>
+      </c>
+      <c r="F5" t="n">
+        <v>116100</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3302</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computer Science </t>
+          <t xml:space="preserve">Civil Engineering </t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>108500</v>
+        <v>99660</v>
       </c>
       <c r="C6" t="n">
-        <v>1597</v>
+        <v>1702</v>
       </c>
       <c r="D6" t="n">
-        <v>101600</v>
+        <v>94370</v>
       </c>
       <c r="E6" t="n">
-        <v>867.3</v>
+        <v>1695</v>
       </c>
       <c r="F6" t="n">
-        <v>128800</v>
+        <v>107500</v>
       </c>
       <c r="G6" t="n">
-        <v>1962</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engineering </t>
+          <t xml:space="preserve">Electrical Engineering </t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100600</v>
+        <v>121600</v>
       </c>
       <c r="C7" t="n">
-        <v>1031</v>
+        <v>1239</v>
       </c>
       <c r="D7" t="n">
-        <v>90490</v>
+        <v>106600</v>
       </c>
       <c r="E7" t="n">
-        <v>2213</v>
+        <v>1062</v>
       </c>
       <c r="F7" t="n">
-        <v>116100</v>
+        <v>139400</v>
       </c>
       <c r="G7" t="n">
-        <v>3302</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Civil Engineering </t>
+          <t xml:space="preserve">Mechanical Engineering </t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>99660</v>
+        <v>106200</v>
       </c>
       <c r="C8" t="n">
-        <v>1702</v>
+        <v>957.2</v>
       </c>
       <c r="D8" t="n">
-        <v>94370</v>
+        <v>99180</v>
       </c>
       <c r="E8" t="n">
-        <v>1695</v>
+        <v>1800</v>
       </c>
       <c r="F8" t="n">
-        <v>107500</v>
+        <v>124900</v>
       </c>
       <c r="G8" t="n">
-        <v>2570</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical Engineering </t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>121600</v>
+        <v>86560</v>
       </c>
       <c r="C9" t="n">
-        <v>1239</v>
+        <v>1476</v>
       </c>
       <c r="D9" t="n">
-        <v>106600</v>
+        <v>76350</v>
       </c>
       <c r="E9" t="n">
-        <v>1062</v>
+        <v>1817</v>
       </c>
       <c r="F9" t="n">
-        <v>139400</v>
+        <v>96530</v>
       </c>
       <c r="G9" t="n">
-        <v>2337</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanical Engineering </t>
+          <t xml:space="preserve">Biology </t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>106200</v>
+        <v>81550</v>
       </c>
       <c r="C10" t="n">
-        <v>957.2</v>
+        <v>706.8</v>
       </c>
       <c r="D10" t="n">
-        <v>99180</v>
+        <v>60390</v>
       </c>
       <c r="E10" t="n">
-        <v>1800</v>
+        <v>983.2</v>
       </c>
       <c r="F10" t="n">
-        <v>124900</v>
+        <v>102800</v>
       </c>
       <c r="G10" t="n">
-        <v>1800</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t xml:space="preserve">Chemistry </t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>86560</v>
+        <v>94680</v>
       </c>
       <c r="C11" t="n">
-        <v>1476</v>
+        <v>2114</v>
       </c>
       <c r="D11" t="n">
-        <v>76350</v>
+        <v>71060</v>
       </c>
       <c r="E11" t="n">
-        <v>1817</v>
+        <v>2374</v>
       </c>
       <c r="F11" t="n">
-        <v>96530</v>
+        <v>109100</v>
       </c>
       <c r="G11" t="n">
-        <v>2155</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biology </t>
+          <t xml:space="preserve">Psychology </t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>81550</v>
+        <v>62270</v>
       </c>
       <c r="C12" t="n">
-        <v>706.8</v>
+        <v>488.2</v>
       </c>
       <c r="D12" t="n">
-        <v>60390</v>
+        <v>52460</v>
       </c>
       <c r="E12" t="n">
-        <v>983.2</v>
+        <v>579.3</v>
       </c>
       <c r="F12" t="n">
-        <v>102800</v>
+        <v>72490</v>
       </c>
       <c r="G12" t="n">
-        <v>1448</v>
+        <v>781.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chemistry </t>
+          <t xml:space="preserve">Economics </t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>94680</v>
+        <v>101400</v>
       </c>
       <c r="C13" t="n">
-        <v>2114</v>
+        <v>916.1</v>
       </c>
       <c r="D13" t="n">
-        <v>71060</v>
+        <v>89570</v>
       </c>
       <c r="E13" t="n">
-        <v>2374</v>
+        <v>2396</v>
       </c>
       <c r="F13" t="n">
-        <v>109100</v>
+        <v>122100</v>
       </c>
       <c r="G13" t="n">
-        <v>3292</v>
+        <v>2864</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psychology </t>
+          <t xml:space="preserve">Political Science </t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>62270</v>
+        <v>86380</v>
       </c>
       <c r="C14" t="n">
-        <v>488.2</v>
+        <v>1325</v>
       </c>
       <c r="D14" t="n">
-        <v>52460</v>
+        <v>72420</v>
       </c>
       <c r="E14" t="n">
-        <v>579.3</v>
+        <v>1853</v>
       </c>
       <c r="F14" t="n">
-        <v>72490</v>
+        <v>102700</v>
       </c>
       <c r="G14" t="n">
-        <v>781.3</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Economics </t>
+          <t xml:space="preserve">Sociology </t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>101400</v>
+        <v>63660</v>
       </c>
       <c r="C15" t="n">
-        <v>916.1</v>
+        <v>836.9</v>
       </c>
       <c r="D15" t="n">
-        <v>89570</v>
+        <v>56700</v>
       </c>
       <c r="E15" t="n">
-        <v>2396</v>
+        <v>1498</v>
       </c>
       <c r="F15" t="n">
-        <v>122100</v>
+        <v>75620</v>
       </c>
       <c r="G15" t="n">
-        <v>2864</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Political Science </t>
+          <t xml:space="preserve">Nursing </t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>86380</v>
+        <v>79600</v>
       </c>
       <c r="C16" t="n">
-        <v>1325</v>
+        <v>812.7</v>
       </c>
       <c r="D16" t="n">
-        <v>72420</v>
+        <v>73560</v>
       </c>
       <c r="E16" t="n">
-        <v>1853</v>
+        <v>545.7</v>
       </c>
       <c r="F16" t="n">
-        <v>102700</v>
+        <v>99060</v>
       </c>
       <c r="G16" t="n">
-        <v>1578</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sociology </t>
+          <t>Other Science and Engineering Degrees2</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>63660</v>
+        <v>77910</v>
       </c>
       <c r="C17" t="n">
-        <v>836.9</v>
+        <v>460.3</v>
       </c>
       <c r="D17" t="n">
-        <v>56700</v>
+        <v>68510</v>
       </c>
       <c r="E17" t="n">
-        <v>1498</v>
+        <v>639.5</v>
       </c>
       <c r="F17" t="n">
-        <v>75620</v>
+        <v>91410</v>
       </c>
       <c r="G17" t="n">
-        <v>1429</v>
+        <v>476.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nursing </t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>79600</v>
-      </c>
-      <c r="C18" t="n">
-        <v>812.7</v>
-      </c>
-      <c r="D18" t="n">
-        <v>73560</v>
-      </c>
-      <c r="E18" t="n">
-        <v>545.7</v>
-      </c>
-      <c r="F18" t="n">
-        <v>99060</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1905</v>
-      </c>
+          <t xml:space="preserve">Business Degrees </t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Other Science and Engineering Degrees2</t>
+          <t xml:space="preserve">General Business </t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>77910</v>
+        <v>80120</v>
       </c>
       <c r="C19" t="n">
-        <v>460.3</v>
+        <v>710.7</v>
       </c>
       <c r="D19" t="n">
-        <v>68510</v>
+        <v>74570</v>
       </c>
       <c r="E19" t="n">
-        <v>639.5</v>
+        <v>819.8</v>
       </c>
       <c r="F19" t="n">
-        <v>91410</v>
+        <v>96280</v>
       </c>
       <c r="G19" t="n">
-        <v>476.9</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Degrees </t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+          <t xml:space="preserve">Accounting </t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>84880</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1051</v>
+      </c>
+      <c r="D20" t="n">
+        <v>77200</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1138</v>
+      </c>
+      <c r="F20" t="n">
+        <v>102000</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1085</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">General Business </t>
+          <t xml:space="preserve">Business Management and Adminstration </t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>80120</v>
+        <v>75600</v>
       </c>
       <c r="C21" t="n">
-        <v>710.7</v>
+        <v>581.2</v>
       </c>
       <c r="D21" t="n">
-        <v>74570</v>
+        <v>71220</v>
       </c>
       <c r="E21" t="n">
-        <v>819.8</v>
+        <v>659.2</v>
       </c>
       <c r="F21" t="n">
-        <v>96280</v>
+        <v>90840</v>
       </c>
       <c r="G21" t="n">
-        <v>1719</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accounting </t>
+          <t xml:space="preserve">Marketing </t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>84880</v>
+        <v>75930</v>
       </c>
       <c r="C22" t="n">
-        <v>1051</v>
+        <v>798.6</v>
       </c>
       <c r="D22" t="n">
-        <v>77200</v>
+        <v>73440</v>
       </c>
       <c r="E22" t="n">
-        <v>1138</v>
+        <v>991.4</v>
       </c>
       <c r="F22" t="n">
-        <v>102000</v>
+        <v>88750</v>
       </c>
       <c r="G22" t="n">
-        <v>1085</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Management and Adminstration </t>
+          <t xml:space="preserve">Finance </t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>75600</v>
+        <v>99900</v>
       </c>
       <c r="C23" t="n">
-        <v>581.2</v>
+        <v>1779</v>
       </c>
       <c r="D23" t="n">
-        <v>71220</v>
+        <v>91400</v>
       </c>
       <c r="E23" t="n">
-        <v>659.2</v>
+        <v>1259</v>
       </c>
       <c r="F23" t="n">
-        <v>90840</v>
+        <v>116100</v>
       </c>
       <c r="G23" t="n">
-        <v>1341</v>
+        <v>3312</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marketing </t>
+          <t xml:space="preserve">Other Business Degrees </t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>75930</v>
+        <v>77160</v>
       </c>
       <c r="C24" t="n">
-        <v>798.6</v>
+        <v>882.2</v>
       </c>
       <c r="D24" t="n">
-        <v>73440</v>
+        <v>72540</v>
       </c>
       <c r="E24" t="n">
-        <v>991.4</v>
+        <v>1113</v>
       </c>
       <c r="F24" t="n">
-        <v>88750</v>
+        <v>92260</v>
       </c>
       <c r="G24" t="n">
-        <v>2792</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finance </t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>99900</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1779</v>
-      </c>
-      <c r="D25" t="n">
-        <v>91400</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1259</v>
-      </c>
-      <c r="F25" t="n">
-        <v>116100</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3312</v>
-      </c>
+          <t xml:space="preserve">Education Degrees </t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Business Degrees </t>
+          <t>General Education</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>77160</v>
+        <v>58000</v>
       </c>
       <c r="C26" t="n">
-        <v>882.2</v>
+        <v>730.8</v>
       </c>
       <c r="D26" t="n">
-        <v>72540</v>
+        <v>50490</v>
       </c>
       <c r="E26" t="n">
-        <v>1113</v>
+        <v>472.6</v>
       </c>
       <c r="F26" t="n">
-        <v>92260</v>
+        <v>66880</v>
       </c>
       <c r="G26" t="n">
-        <v>1993</v>
+        <v>894.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Education Degrees </t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+          <t>Elementary Education</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>54900</v>
+      </c>
+      <c r="C27" t="n">
+        <v>549.8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>47320</v>
+      </c>
+      <c r="E27" t="n">
+        <v>621</v>
+      </c>
+      <c r="F27" t="n">
+        <v>65170</v>
+      </c>
+      <c r="G27" t="n">
+        <v>706.1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>General Education</t>
+          <t>Other Education Degrees</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>58000</v>
+        <v>58120</v>
       </c>
       <c r="C28" t="n">
-        <v>730.8</v>
+        <v>477.6</v>
       </c>
       <c r="D28" t="n">
-        <v>50490</v>
+        <v>49600</v>
       </c>
       <c r="E28" t="n">
-        <v>472.6</v>
+        <v>620.9</v>
       </c>
       <c r="F28" t="n">
-        <v>66880</v>
+        <v>67460</v>
       </c>
       <c r="G28" t="n">
-        <v>894.7</v>
+        <v>645.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Elementary Education</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>54900</v>
-      </c>
-      <c r="C29" t="n">
-        <v>549.8</v>
-      </c>
-      <c r="D29" t="n">
-        <v>47320</v>
-      </c>
-      <c r="E29" t="n">
-        <v>621</v>
-      </c>
-      <c r="F29" t="n">
-        <v>65170</v>
-      </c>
-      <c r="G29" t="n">
-        <v>706.1</v>
-      </c>
+          <t xml:space="preserve">Arts, Humanities and Other Degrees </t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Other Education Degrees</t>
+          <t xml:space="preserve">Communications </t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>58120</v>
+        <v>67840</v>
       </c>
       <c r="C30" t="n">
-        <v>477.6</v>
+        <v>1017</v>
       </c>
       <c r="D30" t="n">
-        <v>49600</v>
+        <v>64760</v>
       </c>
       <c r="E30" t="n">
-        <v>620.9</v>
+        <v>670.6</v>
       </c>
       <c r="F30" t="n">
-        <v>67460</v>
+        <v>76560</v>
       </c>
       <c r="G30" t="n">
-        <v>645.3</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arts, Humanities and Other Degrees </t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+          <t xml:space="preserve">English Language and Literature </t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>65060</v>
+      </c>
+      <c r="C31" t="n">
+        <v>927</v>
+      </c>
+      <c r="D31" t="n">
+        <v>56180</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1198</v>
+      </c>
+      <c r="F31" t="n">
+        <v>75370</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1186</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communications </t>
+          <t xml:space="preserve">Liberal Arts </t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>67840</v>
+        <v>61380</v>
       </c>
       <c r="C32" t="n">
-        <v>1017</v>
+        <v>1044</v>
       </c>
       <c r="D32" t="n">
-        <v>64760</v>
+        <v>54560</v>
       </c>
       <c r="E32" t="n">
-        <v>670.6</v>
+        <v>1350</v>
       </c>
       <c r="F32" t="n">
-        <v>76560</v>
+        <v>77310</v>
       </c>
       <c r="G32" t="n">
-        <v>1216</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">English Language and Literature </t>
+          <t xml:space="preserve">History </t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>65060</v>
+        <v>73560</v>
       </c>
       <c r="C33" t="n">
-        <v>927</v>
+        <v>1006</v>
       </c>
       <c r="D33" t="n">
-        <v>56180</v>
+        <v>62340</v>
       </c>
       <c r="E33" t="n">
-        <v>1198</v>
+        <v>1188</v>
       </c>
       <c r="F33" t="n">
-        <v>75370</v>
+        <v>85160</v>
       </c>
       <c r="G33" t="n">
-        <v>1186</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liberal Arts </t>
+          <t xml:space="preserve">Fine Arts </t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>61380</v>
+        <v>53450</v>
       </c>
       <c r="C34" t="n">
-        <v>1044</v>
+        <v>1303</v>
       </c>
       <c r="D34" t="n">
-        <v>54560</v>
+        <v>50730</v>
       </c>
       <c r="E34" t="n">
-        <v>1350</v>
+        <v>1061</v>
       </c>
       <c r="F34" t="n">
-        <v>77310</v>
+        <v>63200</v>
       </c>
       <c r="G34" t="n">
-        <v>2048</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">History </t>
+          <t xml:space="preserve">Commerical Art and Graphic Design </t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>73560</v>
+        <v>59770</v>
       </c>
       <c r="C35" t="n">
-        <v>1006</v>
+        <v>1049</v>
       </c>
       <c r="D35" t="n">
-        <v>62340</v>
+        <v>58490</v>
       </c>
       <c r="E35" t="n">
-        <v>1188</v>
+        <v>1161</v>
       </c>
       <c r="F35" t="n">
-        <v>85160</v>
+        <v>69310</v>
       </c>
       <c r="G35" t="n">
-        <v>1574</v>
+        <v>4029</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fine Arts </t>
+          <t xml:space="preserve">Family and Consumer Sciences </t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>53450</v>
+        <v>52850</v>
       </c>
       <c r="C36" t="n">
-        <v>1303</v>
+        <v>951.6</v>
       </c>
       <c r="D36" t="n">
-        <v>50730</v>
+        <v>46770</v>
       </c>
       <c r="E36" t="n">
-        <v>1061</v>
+        <v>1477</v>
       </c>
       <c r="F36" t="n">
-        <v>63200</v>
+        <v>63800</v>
       </c>
       <c r="G36" t="n">
-        <v>2194</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commerical Art and Graphic Design </t>
+          <t>Physical Fitness, Parks, Recreation, and Leisure</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>59770</v>
+        <v>61580</v>
       </c>
       <c r="C37" t="n">
-        <v>1049</v>
+        <v>691.3</v>
       </c>
       <c r="D37" t="n">
-        <v>58490</v>
+        <v>55020</v>
       </c>
       <c r="E37" t="n">
-        <v>1161</v>
+        <v>1241</v>
       </c>
       <c r="F37" t="n">
-        <v>69310</v>
+        <v>73180</v>
       </c>
       <c r="G37" t="n">
-        <v>4029</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Family and Consumer Sciences </t>
+          <t>Criminal Justice and Fire Protection</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>52850</v>
+        <v>64690</v>
       </c>
       <c r="C38" t="n">
-        <v>951.6</v>
+        <v>809.2</v>
       </c>
       <c r="D38" t="n">
-        <v>46770</v>
+        <v>61830</v>
       </c>
       <c r="E38" t="n">
-        <v>1477</v>
+        <v>716.4</v>
       </c>
       <c r="F38" t="n">
-        <v>63800</v>
+        <v>76740</v>
       </c>
       <c r="G38" t="n">
-        <v>1587</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Physical Fitness, Parks, Recreation, and Leisure</t>
+          <t xml:space="preserve">Social Work </t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>61580</v>
+        <v>55060</v>
       </c>
       <c r="C39" t="n">
-        <v>691.3</v>
+        <v>838</v>
       </c>
       <c r="D39" t="n">
-        <v>55020</v>
+        <v>46700</v>
       </c>
       <c r="E39" t="n">
-        <v>1241</v>
+        <v>1233</v>
       </c>
       <c r="F39" t="n">
-        <v>73180</v>
+        <v>62510</v>
       </c>
       <c r="G39" t="n">
-        <v>1337</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Criminal Justice and Fire Protection</t>
+          <t xml:space="preserve">Other Degrees </t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>64690</v>
+        <v>62100</v>
       </c>
       <c r="C40" t="n">
-        <v>809.2</v>
+        <v>419.6</v>
       </c>
       <c r="D40" t="n">
-        <v>61830</v>
+        <v>57340</v>
       </c>
       <c r="E40" t="n">
-        <v>716.4</v>
+        <v>786.2</v>
       </c>
       <c r="F40" t="n">
-        <v>76740</v>
+        <v>71220</v>
       </c>
       <c r="G40" t="n">
-        <v>1556</v>
+        <v>917.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Social Work </t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>55060</v>
-      </c>
-      <c r="C41" t="n">
-        <v>838</v>
-      </c>
-      <c r="D41" t="n">
-        <v>46700</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1233</v>
-      </c>
-      <c r="F41" t="n">
-        <v>62510</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1025</v>
-      </c>
+          <t>Source: U.S. Census Bureau, 2022 American Community Survey, 1-year estimates. For more information, refer to &lt;www.census.gov/acs&gt;.</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Degrees </t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>62100</v>
-      </c>
-      <c r="C42" t="n">
-        <v>419.6</v>
-      </c>
-      <c r="D42" t="n">
-        <v>57340</v>
-      </c>
-      <c r="E42" t="n">
-        <v>786.2</v>
-      </c>
-      <c r="F42" t="n">
-        <v>71220</v>
-      </c>
-      <c r="G42" t="n">
-        <v>917.4</v>
-      </c>
+          <t>The Census Bureau has reviewed this data product to ensure appropriate access, use, and disclosure avoidance protection of the confidential source data used to produce this product (Data Management System (DMS) number: P-001-0000001262, Disclosure Review Board (DRB) approval number: CBDRB-FY23-SEHSD003-068.</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Source: U.S. Census Bureau, 2022 American Community Survey, 1-year estimates. For more information, refer to &lt;www.census.gov/acs&gt;.</t>
+          <t xml:space="preserve">Note: 1. We are unable to determine what field respondents pursue an advanced degree in. The field of degree question on the American Community Survey asks about Bachelor's degree. 2. Science and Engineering related fields are included within the "other science and engineering degrees" category. </t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1463,32 +1431,6 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>The Census Bureau has reviewed this data product to ensure appropriate access, use, and disclosure avoidance protection of the confidential source data used to produce this product (Data Management System (DMS) number: P-001-0000001262, Disclosure Review Board (DRB) approval number: CBDRB-FY23-SEHSD003-068.</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Note: 1. We are unable to determine what field respondents pursue an advanced degree in. The field of degree question on the American Community Survey asks about Bachelor's degree. 2. Science and Engineering related fields are included within the "other science and engineering degrees" category. </t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
